--- a/K_fold_Formula.xlsx
+++ b/K_fold_Formula.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Desktop\ML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BDF9C75-1DA0-4905-B930-D8B41A52AE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B6888E-888B-4B76-B760-9F3287747D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="9810" windowHeight="11385" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
   <si>
     <t>Fold</t>
   </si>
@@ -63,6 +65,57 @@
   </si>
   <si>
     <t>Train</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>MAE</t>
+  </si>
+  <si>
+    <t>AARD</t>
+  </si>
+  <si>
+    <t>MARE</t>
+  </si>
+  <si>
+    <t>COV</t>
+  </si>
+  <si>
+    <t>U95</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>MBE</t>
+  </si>
+  <si>
+    <t>LogCoshLoss</t>
+  </si>
+  <si>
+    <t>HuberLoss</t>
+  </si>
+  <si>
+    <t>MAPE</t>
+  </si>
+  <si>
+    <t>COM</t>
+  </si>
+  <si>
+    <t>RAE</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Value-test</t>
   </si>
 </sst>
 </file>
@@ -156,20 +209,33 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good 2" xfId="1" xr:uid="{ADA26BFB-D622-446A-91DE-FAA7BF09EC7E}"/>
@@ -456,176 +522,980 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2">
         <v>0.32315789473684209</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2">
         <v>0.32282183307309059</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2">
         <f>B9-B5</f>
         <v>0.57868421052631569</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2">
         <f>D2+B2</f>
         <v>0.90184210526315778</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2">
         <f>E9-C5</f>
         <v>0.58014521359593751</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2">
         <f>F2+C2</f>
         <v>0.90296704666902805</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3">
         <v>0.33684210526315789</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3">
         <v>0.33724875536619697</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="2">
+      <c r="E3">
         <f>D2+B3</f>
         <v>0.91552631578947352</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="3">
+      <c r="G3">
         <f>F2+C3</f>
         <v>0.91739396896213443</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>0.33684210526315789</v>
+      </c>
+      <c r="C4">
+        <v>0.33610114798658092</v>
+      </c>
+      <c r="E4">
+        <f>D2+B4</f>
+        <v>0.91552631578947352</v>
+      </c>
+      <c r="G4">
+        <f>F2+C4</f>
+        <v>0.91624636158251849</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.35789473684210532</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.35745418181060651</v>
+      </c>
+      <c r="E5">
+        <f>D2+B5</f>
+        <v>0.93657894736842096</v>
+      </c>
+      <c r="G5">
+        <f>F2+C5</f>
+        <v>0.93759939540654402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0.31894736842105259</v>
+      </c>
+      <c r="C6">
+        <v>0.31873042438700178</v>
+      </c>
+      <c r="E6">
+        <f>D2+B6</f>
+        <v>0.89763157894736834</v>
+      </c>
+      <c r="G6">
+        <f>F2+C6</f>
+        <v>0.89887563798293924</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>0.93557894736842107</v>
+      </c>
+      <c r="C8">
+        <v>0.94124789453841462</v>
+      </c>
+      <c r="D8">
+        <v>0.93498451365523527</v>
+      </c>
+      <c r="E8">
+        <v>0.93653466226908533</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>0.93657894736842107</v>
+      </c>
+      <c r="C9">
+        <v>0.94287956730508682</v>
+      </c>
+      <c r="D9">
+        <v>0.93540775056626912</v>
+      </c>
+      <c r="E9">
+        <v>0.93759939540654402</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59F98149-F14F-41F7-8808-041B3BE7E1F6}">
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4">
+        <v>-0.1087788846514435</v>
+      </c>
+      <c r="C2" s="4">
+        <v>4.5355495769160541</v>
+      </c>
+      <c r="D2">
+        <f>B9-B4</f>
+        <v>1.0061893298145765</v>
+      </c>
+      <c r="E2">
+        <f>D2+B2</f>
+        <v>0.89741044516313306</v>
+      </c>
+      <c r="F2">
+        <f>C9-C4</f>
+        <v>-3.3515198827789234</v>
+      </c>
+      <c r="G2">
+        <f>F2+C2</f>
+        <v>1.1840296941371307</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4">
+        <v>-0.1627084410077855</v>
+      </c>
+      <c r="C3" s="4">
+        <v>4.5440528417253656</v>
+      </c>
+      <c r="E3">
+        <f>D2+B3</f>
+        <v>0.84348088880679106</v>
+      </c>
+      <c r="G3">
+        <f>F2+C3</f>
+        <v>1.1925329589464422</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
       <c r="B4" s="6">
-        <v>0.33684210526315789</v>
+        <v>-9.0470251551415526E-2</v>
       </c>
       <c r="C4" s="6">
-        <v>0.33610114798658092</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="2">
+        <v>4.6005448835726694</v>
+      </c>
+      <c r="E4">
         <f>D2+B4</f>
-        <v>0.91552631578947352</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="3">
+        <v>0.91571907826316101</v>
+      </c>
+      <c r="G4">
         <f>F2+C4</f>
-        <v>0.91624636158251849</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+        <v>1.249025000793746</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="8">
-        <v>0.35789473684210532</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.35745418181060651</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="2">
+      <c r="B5" s="4">
+        <v>-0.1299132585130138</v>
+      </c>
+      <c r="C5" s="4">
+        <v>4.5412923688041218</v>
+      </c>
+      <c r="E5">
         <f>D2+B5</f>
-        <v>0.93657894736842096</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="3">
+        <v>0.87627607130156271</v>
+      </c>
+      <c r="G5">
         <f>F2+C5</f>
-        <v>0.93759939540654402</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+        <v>1.1897724860251984</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
-        <v>0.31894736842105259</v>
-      </c>
-      <c r="C6" s="6">
-        <v>0.31873042438700178</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="2">
+      <c r="B6" s="4">
+        <v>-0.1100913704517716</v>
+      </c>
+      <c r="C6" s="4">
+        <v>4.65200522252385</v>
+      </c>
+      <c r="E6">
         <f>D2+B6</f>
-        <v>0.89763157894736834</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="3">
+        <v>0.8960979593628049</v>
+      </c>
+      <c r="G6">
         <f>F2+C6</f>
-        <v>0.89887563798293924</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+        <v>1.3004853397449265</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10">
+        <v>0.91481020640987509</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1.2629699483595891</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1.0953033067827691</v>
+      </c>
+      <c r="E8" s="10">
+        <v>4.1401506000038601</v>
+      </c>
+      <c r="F8" s="10">
+        <v>4.1401506000038601</v>
+      </c>
+      <c r="G8" s="10">
+        <v>4.5848337413751147E-2</v>
+      </c>
+      <c r="H8" s="10">
+        <v>2.0696617891671671</v>
+      </c>
+      <c r="I8" s="10">
+        <v>4.5848337413751147E-2</v>
+      </c>
+      <c r="J8" s="10">
+        <v>2.6319016597690009E-2</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0.58589104163582484</v>
+      </c>
+      <c r="L8" s="10">
+        <v>0.67025698934642453</v>
+      </c>
+      <c r="M8" s="10">
+        <v>4.1401506000038601</v>
+      </c>
+      <c r="N8" s="10">
+        <v>-9.5543298946772031E-4</v>
+      </c>
+      <c r="O8" s="10">
+        <v>0.29137826758062851</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10">
+        <v>0.9157190782631609</v>
+      </c>
+      <c r="C9" s="10">
+        <v>1.249025000793746</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1.081233229648195</v>
+      </c>
+      <c r="E9" s="10">
+        <v>4.066389502007028</v>
+      </c>
+      <c r="F9" s="10">
+        <v>4.066389502007028</v>
+      </c>
+      <c r="G9" s="10">
+        <v>4.5198406363547751E-2</v>
+      </c>
+      <c r="H9" s="10">
+        <v>2.0558029041730919</v>
+      </c>
+      <c r="I9" s="10">
+        <v>4.5198406363547751E-2</v>
+      </c>
+      <c r="J9" s="10">
+        <v>-1.7330765366176659E-10</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0.57484741271896089</v>
+      </c>
+      <c r="L9" s="10">
+        <v>0.65767798315905224</v>
+      </c>
+      <c r="M9" s="10">
+        <v>4.066389502007028</v>
+      </c>
+      <c r="N9" s="10">
+        <v>6.2716823665263706E-12</v>
+      </c>
+      <c r="O9" s="10">
+        <v>0.2896946426268257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="10">
+        <v>0.91067870768869685</v>
+      </c>
+      <c r="C10" s="10">
+        <v>1.317210294456288</v>
+      </c>
+      <c r="D10" s="10">
+        <v>1.1515158621406441</v>
+      </c>
+      <c r="E10" s="10">
+        <v>4.4348398021131947</v>
+      </c>
+      <c r="F10" s="10">
+        <v>4.4348398021131947</v>
+      </c>
+      <c r="G10" s="10">
+        <v>4.8432565301722623E-2</v>
+      </c>
+      <c r="H10" s="10">
+        <v>2.108909892332115</v>
+      </c>
+      <c r="I10" s="10">
+        <v>4.8432565301722623E-2</v>
+      </c>
+      <c r="J10" s="10">
+        <v>0.13146834684329711</v>
+      </c>
+      <c r="K10" s="10">
+        <v>0.63001237770978091</v>
+      </c>
+      <c r="L10" s="10">
+        <v>0.72051244103241086</v>
+      </c>
+      <c r="M10" s="10">
+        <v>4.4348398021131947</v>
+      </c>
+      <c r="N10" s="10">
+        <v>-4.8339656320602444E-3</v>
+      </c>
+      <c r="O10" s="10">
+        <v>0.2990923970764201</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="10">
+        <v>0.91013116401559768</v>
+      </c>
+      <c r="C11" s="10">
+        <v>1.2784931708817</v>
+      </c>
+      <c r="D11" s="10">
+        <v>1.109162767806225</v>
+      </c>
+      <c r="E11" s="10">
+        <v>4.2669536273448996</v>
+      </c>
+      <c r="F11" s="10">
+        <v>4.2669536273448996</v>
+      </c>
+      <c r="G11" s="10">
+        <v>4.7078557863079303E-2</v>
+      </c>
+      <c r="H11" s="10">
+        <v>2.0703065574930002</v>
+      </c>
+      <c r="I11" s="10">
+        <v>4.7078557863079303E-2</v>
+      </c>
+      <c r="J11" s="10">
+        <v>0.1436456047785756</v>
+      </c>
+      <c r="K11" s="10">
+        <v>0.59872566033677665</v>
+      </c>
+      <c r="L11" s="10">
+        <v>0.68566617695048271</v>
+      </c>
+      <c r="M11" s="10">
+        <v>4.2669536273448996</v>
+      </c>
+      <c r="N11" s="10">
+        <v>-5.2895299485106748E-3</v>
+      </c>
+      <c r="O11" s="10">
+        <v>0.29954044509448052</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="10">
+        <v>0.91114542124515163</v>
+      </c>
+      <c r="C12" s="10">
+        <v>1.354702558544493</v>
+      </c>
+      <c r="D12" s="10">
+        <v>1.193733209377837</v>
+      </c>
+      <c r="E12" s="10">
+        <v>4.6021878801674898</v>
+      </c>
+      <c r="F12" s="10">
+        <v>4.6021878801674898</v>
+      </c>
+      <c r="G12" s="10">
+        <v>4.9737840909622598E-2</v>
+      </c>
+      <c r="H12" s="10">
+        <v>2.1365579168907098</v>
+      </c>
+      <c r="I12" s="10">
+        <v>4.9737840909622598E-2</v>
+      </c>
+      <c r="J12" s="10">
+        <v>0.119330118580888</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0.66119881714248696</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0.75524701837048669</v>
+      </c>
+      <c r="M12" s="10">
+        <v>4.6021878801674898</v>
+      </c>
+      <c r="N12" s="10">
+        <v>-4.3811997078379008E-3</v>
+      </c>
+      <c r="O12" s="10">
+        <v>0.29867385163325</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263A6AFC-A56D-462B-BBBB-27D930AA82E3}">
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="B2" s="7">
+        <v>-0.1036643070278882</v>
+      </c>
+      <c r="C2" s="7">
+        <v>4.550461619614282</v>
+      </c>
+      <c r="D2">
+        <f>B9-B4</f>
+        <v>0.97153299032948659</v>
+      </c>
+      <c r="E2">
+        <f>D2+B2</f>
+        <v>0.86786868330159839</v>
+      </c>
+      <c r="F2">
+        <f>C9-C4</f>
+        <v>-3.1112621093442154</v>
+      </c>
+      <c r="G2">
+        <f>F2+C2</f>
+        <v>1.4391995102700665</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7">
+        <v>-0.14287696598522431</v>
+      </c>
+      <c r="C3" s="7">
+        <v>4.5163471662739587</v>
+      </c>
+      <c r="E3">
+        <f>D2+B3</f>
+        <v>0.82865602434426222</v>
+      </c>
+      <c r="G3">
+        <f>F2+C3</f>
+        <v>1.4050850569297433</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9">
+        <v>-9.3204903954542173E-2</v>
+      </c>
+      <c r="C4" s="9">
+        <v>4.6163616297937553</v>
+      </c>
+      <c r="E4">
+        <f>D2+B4</f>
+        <v>0.87832808637494442</v>
+      </c>
+      <c r="G4">
+        <f>F2+C4</f>
+        <v>1.5050995204495399</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="B5" s="7">
+        <v>-0.1221182961965894</v>
+      </c>
+      <c r="C5" s="7">
+        <v>4.5380251121012609</v>
+      </c>
+      <c r="E5">
+        <f>D2+B5</f>
+        <v>0.84941469413289716</v>
+      </c>
+      <c r="G5">
+        <f>F2+C5</f>
+        <v>1.4267630027570455</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="B6" s="7">
+        <v>-0.1072756816212785</v>
+      </c>
+      <c r="C6" s="7">
+        <v>4.649146557129554</v>
+      </c>
+      <c r="E6">
+        <f>D2+B6</f>
+        <v>0.86425730870820805</v>
+      </c>
+      <c r="G6">
+        <f>F2+C6</f>
+        <v>1.5378844477853386</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
-        <v>0.93557894736842107</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.94124789453841462</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0.93498451365523527</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0.93653466226908533</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="B8" s="12">
+        <v>0.87489451351237368</v>
+      </c>
+      <c r="C8" s="12">
+        <v>1.5343704441306869</v>
+      </c>
+      <c r="D8" s="12">
+        <v>1.3306611380129949</v>
+      </c>
+      <c r="E8" s="12">
+        <v>5.0246136115981894</v>
+      </c>
+      <c r="F8" s="12">
+        <v>5.0246136115981894</v>
+      </c>
+      <c r="G8" s="12">
+        <v>5.5651480855023673E-2</v>
+      </c>
+      <c r="H8" s="12">
+        <v>2.5062525883688029</v>
+      </c>
+      <c r="I8" s="12">
+        <v>5.5651480855023673E-2</v>
+      </c>
+      <c r="J8" s="12">
+        <v>2.6736161993923351E-2</v>
+      </c>
+      <c r="K8" s="12">
+        <v>0.78988205364634068</v>
+      </c>
+      <c r="L8" s="12">
+        <v>0.89239791770425181</v>
+      </c>
+      <c r="M8" s="12">
+        <v>5.0246136115981894</v>
+      </c>
+      <c r="N8" s="12">
+        <v>-9.697182404896197E-4</v>
+      </c>
+      <c r="O8" s="12">
+        <v>0.35282771649587591</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4">
-        <v>0.93657894736842107</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0.94287956730508682</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0.93540775056626912</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0.93759939540654402</v>
+      <c r="B9" s="12">
+        <v>0.87832808637494442</v>
+      </c>
+      <c r="C9" s="12">
+        <v>1.5050995204495401</v>
+      </c>
+      <c r="D9" s="12">
+        <v>1.305537226948184</v>
+      </c>
+      <c r="E9" s="12">
+        <v>4.9099069499077617</v>
+      </c>
+      <c r="F9" s="12">
+        <v>4.9099069499077617</v>
+      </c>
+      <c r="G9" s="12">
+        <v>5.4444575902406277E-2</v>
+      </c>
+      <c r="H9" s="12">
+        <v>2.4797247017139288</v>
+      </c>
+      <c r="I9" s="12">
+        <v>5.4444575902406277E-2</v>
+      </c>
+      <c r="J9" s="12">
+        <v>2.1590156024310181E-10</v>
+      </c>
+      <c r="K9" s="12">
+        <v>0.76721589603949336</v>
+      </c>
+      <c r="L9" s="12">
+        <v>0.86792646624887293</v>
+      </c>
+      <c r="M9" s="12">
+        <v>4.9099069499077617</v>
+      </c>
+      <c r="N9" s="12">
+        <v>-7.8096933246514564E-12</v>
+      </c>
+      <c r="O9" s="12">
+        <v>0.34821605156018731</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="12">
+        <v>0.8611159116404159</v>
+      </c>
+      <c r="C10" s="12">
+        <v>1.6460931155026131</v>
+      </c>
+      <c r="D10" s="12">
+        <v>1.4310035876925771</v>
+      </c>
+      <c r="E10" s="12">
+        <v>5.4827408274959328</v>
+      </c>
+      <c r="F10" s="12">
+        <v>5.4827408274959328</v>
+      </c>
+      <c r="G10" s="12">
+        <v>6.0346659127954998E-2</v>
+      </c>
+      <c r="H10" s="12">
+        <v>2.6374420269654459</v>
+      </c>
+      <c r="I10" s="12">
+        <v>6.0346659127954998E-2</v>
+      </c>
+      <c r="J10" s="12">
+        <v>0.1335177837293153</v>
+      </c>
+      <c r="K10" s="12">
+        <v>0.8804084757956393</v>
+      </c>
+      <c r="L10" s="12">
+        <v>0.99013450735835651</v>
+      </c>
+      <c r="M10" s="12">
+        <v>5.4827408274959328</v>
+      </c>
+      <c r="N10" s="12">
+        <v>-4.8948337772332338E-3</v>
+      </c>
+      <c r="O10" s="12">
+        <v>0.37169458298507901</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="12">
+        <v>0.85936728113202665</v>
+      </c>
+      <c r="C11" s="12">
+        <v>1.6185321792168741</v>
+      </c>
+      <c r="D11" s="12">
+        <v>1.3939066824203981</v>
+      </c>
+      <c r="E11" s="12">
+        <v>5.3181766459399391</v>
+      </c>
+      <c r="F11" s="12">
+        <v>5.3181766459399391</v>
+      </c>
+      <c r="G11" s="12">
+        <v>5.9251822581463082E-2</v>
+      </c>
+      <c r="H11" s="12">
+        <v>2.6279666794025029</v>
+      </c>
+      <c r="I11" s="12">
+        <v>5.9251822581463082E-2</v>
+      </c>
+      <c r="J11" s="12">
+        <v>0.1170586159516717</v>
+      </c>
+      <c r="K11" s="12">
+        <v>0.85251151074185383</v>
+      </c>
+      <c r="L11" s="12">
+        <v>0.95858035085410243</v>
+      </c>
+      <c r="M11" s="12">
+        <v>5.3181766459399391</v>
+      </c>
+      <c r="N11" s="12">
+        <v>-4.2853249586648403E-3</v>
+      </c>
+      <c r="O11" s="12">
+        <v>0.37350003417522298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="12">
+        <v>0.86269286632734998</v>
+      </c>
+      <c r="C12" s="12">
+        <v>1.673200129885744</v>
+      </c>
+      <c r="D12" s="12">
+        <v>1.4681004929647561</v>
+      </c>
+      <c r="E12" s="12">
+        <v>5.6473050090519266</v>
+      </c>
+      <c r="F12" s="12">
+        <v>5.6473050090519266</v>
+      </c>
+      <c r="G12" s="12">
+        <v>6.1427955788153847E-2</v>
+      </c>
+      <c r="H12" s="12">
+        <v>2.6435100728751411</v>
+      </c>
+      <c r="I12" s="12">
+        <v>6.1427955788153847E-2</v>
+      </c>
+      <c r="J12" s="12">
+        <v>0.14997695150695889</v>
+      </c>
+      <c r="K12" s="12">
+        <v>0.90830544084942466</v>
+      </c>
+      <c r="L12" s="12">
+        <v>1.021688663862611</v>
+      </c>
+      <c r="M12" s="12">
+        <v>5.6473050090519266</v>
+      </c>
+      <c r="N12" s="12">
+        <v>-5.5060822563054784E-3</v>
+      </c>
+      <c r="O12" s="12">
+        <v>0.37016788936014289</v>
       </c>
     </row>
   </sheetData>

--- a/K_fold_Formula.xlsx
+++ b/K_fold_Formula.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Desktop\ML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B6888E-888B-4B76-B760-9F3287747D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C86E24-9C19-4E21-BF82-037E4D950435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="9810" windowHeight="11385" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="9810" windowHeight="11385" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet5" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet6" sheetId="7" r:id="rId5"/>
+    <sheet name="Sheet7" sheetId="8" r:id="rId6"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="31">
   <si>
     <t>Fold</t>
   </si>
@@ -116,13 +120,28 @@
   </si>
   <si>
     <t>Value-test</t>
+  </si>
+  <si>
+    <t>F1 _core</t>
+  </si>
+  <si>
+    <t>ETC</t>
+  </si>
+  <si>
+    <t>R_2</t>
+  </si>
+  <si>
+    <t>MARD</t>
+  </si>
+  <si>
+    <t>TRAIN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,8 +168,38 @@
       <sz val="11"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -176,6 +225,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -209,7 +270,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -218,22 +279,31 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -697,24 +767,24 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2">
         <v>-0.1087788846514435</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2">
         <v>4.5355495769160541</v>
       </c>
       <c r="D2">
@@ -735,13 +805,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>-0.1627084410077855</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3">
         <v>4.5440528417253656</v>
       </c>
       <c r="E3">
@@ -754,13 +824,13 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>-9.0470251551415526E-2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>4.6005448835726694</v>
       </c>
       <c r="E4">
@@ -773,13 +843,13 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>-0.1299132585130138</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5">
         <v>4.5412923688041218</v>
       </c>
       <c r="E5">
@@ -792,13 +862,13 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>-0.1100913704517716</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6">
         <v>4.65200522252385</v>
       </c>
       <c r="E6">
@@ -811,284 +881,284 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8">
         <v>0.91481020640987509</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8">
         <v>1.2629699483595891</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8">
         <v>1.0953033067827691</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8">
         <v>4.1401506000038601</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8">
         <v>4.1401506000038601</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8">
         <v>4.5848337413751147E-2</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8">
         <v>2.0696617891671671</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8">
         <v>4.5848337413751147E-2</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8">
         <v>2.6319016597690009E-2</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8">
         <v>0.58589104163582484</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8">
         <v>0.67025698934642453</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8">
         <v>4.1401506000038601</v>
       </c>
-      <c r="N8" s="10">
+      <c r="N8">
         <v>-9.5543298946772031E-4</v>
       </c>
-      <c r="O8" s="10">
+      <c r="O8">
         <v>0.29137826758062851</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9">
         <v>0.9157190782631609</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9">
         <v>1.249025000793746</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9">
         <v>1.081233229648195</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9">
         <v>4.066389502007028</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9">
         <v>4.066389502007028</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9">
         <v>4.5198406363547751E-2</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9">
         <v>2.0558029041730919</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9">
         <v>4.5198406363547751E-2</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9">
         <v>-1.7330765366176659E-10</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9">
         <v>0.57484741271896089</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9">
         <v>0.65767798315905224</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9">
         <v>4.066389502007028</v>
       </c>
-      <c r="N9" s="10">
+      <c r="N9">
         <v>6.2716823665263706E-12</v>
       </c>
-      <c r="O9" s="10">
+      <c r="O9">
         <v>0.2896946426268257</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10">
         <v>0.91067870768869685</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10">
         <v>1.317210294456288</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10">
         <v>1.1515158621406441</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10">
         <v>4.4348398021131947</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10">
         <v>4.4348398021131947</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10">
         <v>4.8432565301722623E-2</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10">
         <v>2.108909892332115</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10">
         <v>4.8432565301722623E-2</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10">
         <v>0.13146834684329711</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10">
         <v>0.63001237770978091</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10">
         <v>0.72051244103241086</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10">
         <v>4.4348398021131947</v>
       </c>
-      <c r="N10" s="10">
+      <c r="N10">
         <v>-4.8339656320602444E-3</v>
       </c>
-      <c r="O10" s="10">
+      <c r="O10">
         <v>0.2990923970764201</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11">
         <v>0.91013116401559768</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11">
         <v>1.2784931708817</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11">
         <v>1.109162767806225</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11">
         <v>4.2669536273448996</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11">
         <v>4.2669536273448996</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11">
         <v>4.7078557863079303E-2</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11">
         <v>2.0703065574930002</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11">
         <v>4.7078557863079303E-2</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11">
         <v>0.1436456047785756</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11">
         <v>0.59872566033677665</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11">
         <v>0.68566617695048271</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11">
         <v>4.2669536273448996</v>
       </c>
-      <c r="N11" s="10">
+      <c r="N11">
         <v>-5.2895299485106748E-3</v>
       </c>
-      <c r="O11" s="10">
+      <c r="O11">
         <v>0.29954044509448052</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12">
         <v>0.91114542124515163</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12">
         <v>1.354702558544493</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12">
         <v>1.193733209377837</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12">
         <v>4.6021878801674898</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12">
         <v>4.6021878801674898</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12">
         <v>4.9737840909622598E-2</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12">
         <v>2.1365579168907098</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12">
         <v>4.9737840909622598E-2</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12">
         <v>0.119330118580888</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12">
         <v>0.66119881714248696</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12">
         <v>0.75524701837048669</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12">
         <v>4.6021878801674898</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12">
         <v>-4.3811997078379008E-3</v>
       </c>
-      <c r="O12" s="10">
+      <c r="O12">
         <v>0.29867385163325</v>
       </c>
     </row>
@@ -1103,24 +1173,24 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2">
         <v>-0.1036643070278882</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2">
         <v>4.550461619614282</v>
       </c>
       <c r="D2">
@@ -1141,13 +1211,13 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3">
         <v>-0.14287696598522431</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3">
         <v>4.5163471662739587</v>
       </c>
       <c r="E3">
@@ -1160,13 +1230,13 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="3">
         <v>-9.3204903954542173E-2</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="3">
         <v>4.6163616297937553</v>
       </c>
       <c r="E4">
@@ -1179,13 +1249,13 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>-0.1221182961965894</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5">
         <v>4.5380251121012609</v>
       </c>
       <c r="E5">
@@ -1198,13 +1268,13 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6">
         <v>-0.1072756816212785</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6">
         <v>4.649146557129554</v>
       </c>
       <c r="E6">
@@ -1217,285 +1287,1114 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M7" s="13" t="s">
+      <c r="M7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N7" s="13" t="s">
+      <c r="N7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="O7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8">
         <v>0.87489451351237368</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8">
         <v>1.5343704441306869</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8">
         <v>1.3306611380129949</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8">
         <v>5.0246136115981894</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8">
         <v>5.0246136115981894</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8">
         <v>5.5651480855023673E-2</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8">
         <v>2.5062525883688029</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8">
         <v>5.5651480855023673E-2</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8">
         <v>2.6736161993923351E-2</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8">
         <v>0.78988205364634068</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8">
         <v>0.89239791770425181</v>
       </c>
-      <c r="M8" s="12">
+      <c r="M8">
         <v>5.0246136115981894</v>
       </c>
-      <c r="N8" s="12">
+      <c r="N8">
         <v>-9.697182404896197E-4</v>
       </c>
-      <c r="O8" s="12">
+      <c r="O8">
         <v>0.35282771649587591</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9">
         <v>0.87832808637494442</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9">
         <v>1.5050995204495401</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9">
         <v>1.305537226948184</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9">
         <v>4.9099069499077617</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9">
         <v>4.9099069499077617</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9">
         <v>5.4444575902406277E-2</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9">
         <v>2.4797247017139288</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9">
         <v>5.4444575902406277E-2</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9">
         <v>2.1590156024310181E-10</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9">
         <v>0.76721589603949336</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9">
         <v>0.86792646624887293</v>
       </c>
-      <c r="M9" s="12">
+      <c r="M9">
         <v>4.9099069499077617</v>
       </c>
-      <c r="N9" s="12">
+      <c r="N9">
         <v>-7.8096933246514564E-12</v>
       </c>
-      <c r="O9" s="12">
+      <c r="O9">
         <v>0.34821605156018731</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
+      <c r="B10">
+        <v>0.8611159116404159</v>
+      </c>
+      <c r="C10">
+        <v>1.6460931155026131</v>
+      </c>
+      <c r="D10">
+        <v>1.4310035876925771</v>
+      </c>
+      <c r="E10">
+        <v>5.4827408274959328</v>
+      </c>
+      <c r="F10">
+        <v>5.4827408274959328</v>
+      </c>
+      <c r="G10">
+        <v>6.0346659127954998E-2</v>
+      </c>
+      <c r="H10">
+        <v>2.6374420269654459</v>
+      </c>
+      <c r="I10">
+        <v>6.0346659127954998E-2</v>
+      </c>
+      <c r="J10">
+        <v>0.1335177837293153</v>
+      </c>
+      <c r="K10">
+        <v>0.8804084757956393</v>
+      </c>
+      <c r="L10">
+        <v>0.99013450735835651</v>
+      </c>
+      <c r="M10">
+        <v>5.4827408274959328</v>
+      </c>
+      <c r="N10">
+        <v>-4.8948337772332338E-3</v>
+      </c>
+      <c r="O10">
+        <v>0.37169458298507901</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11">
+        <v>0.85936728113202665</v>
+      </c>
+      <c r="C11">
+        <v>1.6185321792168741</v>
+      </c>
+      <c r="D11">
+        <v>1.3939066824203981</v>
+      </c>
+      <c r="E11">
+        <v>5.3181766459399391</v>
+      </c>
+      <c r="F11">
+        <v>5.3181766459399391</v>
+      </c>
+      <c r="G11">
+        <v>5.9251822581463082E-2</v>
+      </c>
+      <c r="H11">
+        <v>2.6279666794025029</v>
+      </c>
+      <c r="I11">
+        <v>5.9251822581463082E-2</v>
+      </c>
+      <c r="J11">
+        <v>0.1170586159516717</v>
+      </c>
+      <c r="K11">
+        <v>0.85251151074185383</v>
+      </c>
+      <c r="L11">
+        <v>0.95858035085410243</v>
+      </c>
+      <c r="M11">
+        <v>5.3181766459399391</v>
+      </c>
+      <c r="N11">
+        <v>-4.2853249586648403E-3</v>
+      </c>
+      <c r="O11">
+        <v>0.37350003417522298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12">
+        <v>0.86269286632734998</v>
+      </c>
+      <c r="C12">
+        <v>1.673200129885744</v>
+      </c>
+      <c r="D12">
+        <v>1.4681004929647561</v>
+      </c>
+      <c r="E12">
+        <v>5.6473050090519266</v>
+      </c>
+      <c r="F12">
+        <v>5.6473050090519266</v>
+      </c>
+      <c r="G12">
+        <v>6.1427955788153847E-2</v>
+      </c>
+      <c r="H12">
+        <v>2.6435100728751411</v>
+      </c>
+      <c r="I12">
+        <v>6.1427955788153847E-2</v>
+      </c>
+      <c r="J12">
+        <v>0.14997695150695889</v>
+      </c>
+      <c r="K12">
+        <v>0.90830544084942466</v>
+      </c>
+      <c r="L12">
+        <v>1.021688663862611</v>
+      </c>
+      <c r="M12">
+        <v>5.6473050090519266</v>
+      </c>
+      <c r="N12">
+        <v>-5.5060822563054784E-3</v>
+      </c>
+      <c r="O12">
+        <v>0.37016788936014289</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BACB3318-EC6C-465E-844A-2F6106269962}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4.35897858264368E-2</v>
+      </c>
+      <c r="C2">
+        <v>1.915921443368789</v>
+      </c>
+      <c r="D2">
+        <f>A9-B2</f>
+        <v>0.89724567609209815</v>
+      </c>
+      <c r="E2">
+        <f>D2+B2</f>
+        <v>0.94083546191853495</v>
+      </c>
+      <c r="F2">
+        <f>C2-C9</f>
+        <v>1.3205686289624952</v>
+      </c>
+      <c r="G2">
+        <f>F2+C2</f>
+        <v>3.2364900723312839</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>-0.36842880210970491</v>
+      </c>
+      <c r="C3">
+        <v>2.7290744961685931</v>
+      </c>
+      <c r="E3">
+        <f>D2+B3</f>
+        <v>0.5288168739823933</v>
+      </c>
+      <c r="G3">
+        <f>F2+C3</f>
+        <v>4.0496431251310883</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>-0.2238698310573424</v>
+      </c>
+      <c r="C4">
+        <v>2.6725120539651379</v>
+      </c>
+      <c r="E4">
+        <f>D2+B4</f>
+        <v>0.67337584503475578</v>
+      </c>
+      <c r="G4">
+        <f>F2+C4</f>
+        <v>3.9930806829276331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>-6.9614758460970982E-2</v>
+      </c>
+      <c r="C5">
+        <v>2.4524414933030201</v>
+      </c>
+      <c r="E5">
+        <f>D2+B5</f>
+        <v>0.82763091763112717</v>
+      </c>
+      <c r="G5">
+        <f>F2+C5</f>
+        <v>3.7730101222655152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>-0.14405247710861691</v>
+      </c>
+      <c r="C6">
+        <v>3.039342202521476</v>
+      </c>
+      <c r="E6">
+        <f>D2+B6</f>
+        <v>0.75319319898348125</v>
+      </c>
+      <c r="G6">
+        <f>F2+C6</f>
+        <v>4.3599108314839707</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>0.94083546191853495</v>
+      </c>
+      <c r="B9" s="5">
+        <v>8.5030352140805093E-2</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.59535281440629395</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0.17129745128484</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1.64653217074836</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA8F16B-C411-455E-A7C3-4FF272CC42B6}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1.2179932096260671E-2</v>
+      </c>
+      <c r="C2">
+        <v>1.9471280703689919</v>
+      </c>
+      <c r="D2">
+        <f>A10-B2</f>
+        <v>0.96291501835652438</v>
+      </c>
+      <c r="E2">
+        <f>D2+B2</f>
+        <v>0.97509495045278505</v>
+      </c>
+      <c r="F2">
+        <f>C10-C2</f>
+        <v>-1.5832966445585619</v>
+      </c>
+      <c r="G2">
+        <f>F2+C2</f>
+        <v>0.36383142581043004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>-0.23394828804359991</v>
+      </c>
+      <c r="C3">
+        <v>2.5915092751022639</v>
+      </c>
+      <c r="E3">
+        <f>D2+B3</f>
+        <v>0.72896673031292447</v>
+      </c>
+      <c r="G3">
+        <f>F2+C3</f>
+        <v>1.008212630543702</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>-0.1873632876036162</v>
+      </c>
+      <c r="C4">
+        <v>2.6323514144603308</v>
+      </c>
+      <c r="E4">
+        <f>D2+B4</f>
+        <v>0.77555173075290817</v>
+      </c>
+      <c r="G4">
+        <f>F2+C4</f>
+        <v>1.0490547699017689</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>-5.9758499820929727E-2</v>
+      </c>
+      <c r="C5">
+        <v>2.4411159949591279</v>
+      </c>
+      <c r="E5">
+        <f>D2+B5</f>
+        <v>0.90315651853559464</v>
+      </c>
+      <c r="G5">
+        <f>F2+C5</f>
+        <v>0.85781935040056601</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>-5.3546043260508158E-2</v>
+      </c>
+      <c r="C6">
+        <v>2.9166437621017169</v>
+      </c>
+      <c r="E6">
+        <f>D2+B6</f>
+        <v>0.90936897509601622</v>
+      </c>
+      <c r="G6">
+        <f>F2+C6</f>
+        <v>1.333347117543155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="12">
+        <v>0.97509495045278505</v>
+      </c>
       <c r="B10" s="12">
-        <v>0.8611159116404159</v>
+        <v>5.5207762615011299E-2</v>
       </c>
       <c r="C10" s="12">
-        <v>1.6460931155026131</v>
+        <v>0.36383142581042999</v>
       </c>
       <c r="D10" s="12">
-        <v>1.4310035876925771</v>
+        <v>0.113116235638441</v>
       </c>
       <c r="E10" s="12">
-        <v>5.4827408274959328</v>
-      </c>
-      <c r="F10" s="12">
-        <v>5.4827408274959328</v>
-      </c>
-      <c r="G10" s="12">
-        <v>6.0346659127954998E-2</v>
-      </c>
-      <c r="H10" s="12">
-        <v>2.6374420269654459</v>
-      </c>
-      <c r="I10" s="12">
-        <v>6.0346659127954998E-2</v>
-      </c>
-      <c r="J10" s="12">
-        <v>0.1335177837293153</v>
-      </c>
-      <c r="K10" s="12">
-        <v>0.8804084757956393</v>
-      </c>
-      <c r="L10" s="12">
-        <v>0.99013450735835651</v>
-      </c>
-      <c r="M10" s="12">
-        <v>5.4827408274959328</v>
-      </c>
-      <c r="N10" s="12">
-        <v>-4.8948337772332338E-3</v>
-      </c>
-      <c r="O10" s="12">
-        <v>0.37169458298507901</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="12">
-        <v>0.85936728113202665</v>
-      </c>
-      <c r="C11" s="12">
-        <v>1.6185321792168741</v>
-      </c>
-      <c r="D11" s="12">
-        <v>1.3939066824203981</v>
-      </c>
-      <c r="E11" s="12">
-        <v>5.3181766459399391</v>
-      </c>
-      <c r="F11" s="12">
-        <v>5.3181766459399391</v>
-      </c>
-      <c r="G11" s="12">
-        <v>5.9251822581463082E-2</v>
-      </c>
-      <c r="H11" s="12">
-        <v>2.6279666794025029</v>
-      </c>
-      <c r="I11" s="12">
-        <v>5.9251822581463082E-2</v>
-      </c>
-      <c r="J11" s="12">
-        <v>0.1170586159516717</v>
-      </c>
-      <c r="K11" s="12">
-        <v>0.85251151074185383</v>
-      </c>
-      <c r="L11" s="12">
-        <v>0.95858035085410243</v>
-      </c>
-      <c r="M11" s="12">
-        <v>5.3181766459399391</v>
-      </c>
-      <c r="N11" s="12">
-        <v>-4.2853249586648403E-3</v>
-      </c>
-      <c r="O11" s="12">
-        <v>0.37350003417522298</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0.86269286632734998</v>
-      </c>
-      <c r="C12" s="12">
-        <v>1.673200129885744</v>
-      </c>
-      <c r="D12" s="12">
-        <v>1.4681004929647561</v>
-      </c>
-      <c r="E12" s="12">
-        <v>5.6473050090519266</v>
-      </c>
-      <c r="F12" s="12">
-        <v>5.6473050090519266</v>
-      </c>
-      <c r="G12" s="12">
-        <v>6.1427955788153847E-2</v>
-      </c>
-      <c r="H12" s="12">
-        <v>2.6435100728751411</v>
-      </c>
-      <c r="I12" s="12">
-        <v>6.1427955788153847E-2</v>
-      </c>
-      <c r="J12" s="12">
-        <v>0.14997695150695889</v>
-      </c>
-      <c r="K12" s="12">
-        <v>0.90830544084942466</v>
-      </c>
-      <c r="L12" s="12">
-        <v>1.021688663862611</v>
-      </c>
-      <c r="M12" s="12">
-        <v>5.6473050090519266</v>
-      </c>
-      <c r="N12" s="12">
-        <v>-5.5060822563054784E-3</v>
-      </c>
-      <c r="O12" s="12">
-        <v>0.37016788936014289</v>
+        <v>1.0084709778582299</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A8:E8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E4B81B-66F9-445F-B0C7-874CBAD64040}">
+  <dimension ref="A1:O10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>3.474828746998448E-3</v>
+      </c>
+      <c r="C2">
+        <v>1.955688724619703</v>
+      </c>
+      <c r="D2">
+        <f>B10-B4</f>
+        <v>0.92515462272733251</v>
+      </c>
+      <c r="E2">
+        <f>D2+B2</f>
+        <v>0.92862945147433096</v>
+      </c>
+      <c r="F2">
+        <f>C10-C4</f>
+        <v>-1.8361083613399414</v>
+      </c>
+      <c r="G2">
+        <f>F2+C2</f>
+        <v>0.11958036327976163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>-0.45872691794856779</v>
+      </c>
+      <c r="C3">
+        <v>2.8176775139981611</v>
+      </c>
+      <c r="E3">
+        <f>D2+B3</f>
+        <v>0.46642770477876472</v>
+      </c>
+      <c r="G3">
+        <f>F2+C3</f>
+        <v>0.98156915265821976</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2.4340432124111411E-2</v>
+      </c>
+      <c r="C4">
+        <v>2.3861690697453568</v>
+      </c>
+      <c r="E4">
+        <f>D2+B4</f>
+        <v>0.94949505485144392</v>
+      </c>
+      <c r="G4">
+        <f>F2+C4</f>
+        <v>0.55006070840541543</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>-3.0360235666091469E-2</v>
+      </c>
+      <c r="C5">
+        <v>2.4070189365432921</v>
+      </c>
+      <c r="E5">
+        <f>D2+B5</f>
+        <v>0.89479438706124104</v>
+      </c>
+      <c r="G5">
+        <f>F2+C5</f>
+        <v>0.57091057520335076</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>-2.5533030262719691E-2</v>
+      </c>
+      <c r="C6">
+        <v>2.8776068187025619</v>
+      </c>
+      <c r="E6">
+        <f>D2+B6</f>
+        <v>0.89962159246461282</v>
+      </c>
+      <c r="G6">
+        <f>F2+C6</f>
+        <v>1.0414984573626205</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.95127960424354907</v>
+      </c>
+      <c r="C9">
+        <v>0.536410609867774</v>
+      </c>
+      <c r="D9">
+        <v>0.44203530824503501</v>
+      </c>
+      <c r="E9">
+        <v>11.224227301203319</v>
+      </c>
+      <c r="F9">
+        <v>11.224227301203319</v>
+      </c>
+      <c r="G9">
+        <v>9.9825300297849542E-2</v>
+      </c>
+      <c r="H9">
+        <v>1.0530479595030531</v>
+      </c>
+      <c r="I9">
+        <v>9.9825300297849542E-2</v>
+      </c>
+      <c r="J9">
+        <v>1.894665295110071E-2</v>
+      </c>
+      <c r="K9">
+        <v>0.13028673426429499</v>
+      </c>
+      <c r="L9">
+        <v>0.14332240957558379</v>
+      </c>
+      <c r="M9">
+        <v>11.224227301203319</v>
+      </c>
+      <c r="N9">
+        <v>-3.5259468878685559E-3</v>
+      </c>
+      <c r="O9">
+        <v>0.21236911429327601</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.94949505485144392</v>
+      </c>
+      <c r="C10">
+        <v>0.55006070840541543</v>
+      </c>
+      <c r="D10">
+        <v>0.45074803236211203</v>
+      </c>
+      <c r="E10">
+        <v>11.49394325431963</v>
+      </c>
+      <c r="F10">
+        <v>11.49394325431963</v>
+      </c>
+      <c r="G10">
+        <v>0.1011164369661529</v>
+      </c>
+      <c r="H10">
+        <v>1.069216242294895</v>
+      </c>
+      <c r="I10">
+        <v>0.1011164369661529</v>
+      </c>
+      <c r="J10">
+        <v>5.2074023476651229E-2</v>
+      </c>
+      <c r="K10">
+        <v>0.1363966268025848</v>
+      </c>
+      <c r="L10">
+        <v>0.15060118944851511</v>
+      </c>
+      <c r="M10">
+        <v>11.49394325431963</v>
+      </c>
+      <c r="N10">
+        <v>-9.5726519491188353E-3</v>
+      </c>
+      <c r="O10">
+        <v>0.2124247083824832</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FFA4D62-EA70-4E4C-A594-D58C5B00EF5C}">
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>0.4</v>
+      </c>
+      <c r="C2">
+        <v>0.34468899521531099</v>
+      </c>
+      <c r="D2">
+        <f>B19-B2</f>
+        <v>0.53749999999999998</v>
+      </c>
+      <c r="E2">
+        <f>D2+B2</f>
+        <v>0.9375</v>
+      </c>
+      <c r="F2">
+        <f>E19-C2</f>
+        <v>0.58958043905412327</v>
+      </c>
+      <c r="G2">
+        <f>F2+C2</f>
+        <v>0.93426943426943421</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0.35</v>
+      </c>
+      <c r="C3">
+        <v>0.34166666666666667</v>
+      </c>
+      <c r="E3">
+        <f>D2+B3</f>
+        <v>0.88749999999999996</v>
+      </c>
+      <c r="G3">
+        <f>F2+C3</f>
+        <v>0.93124710572078995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>0.4</v>
+      </c>
+      <c r="C4">
+        <v>0.40686274509803921</v>
+      </c>
+      <c r="E4">
+        <f>D2+B4</f>
+        <v>0.9375</v>
+      </c>
+      <c r="G4">
+        <f>F2+C4</f>
+        <v>0.99644318415216249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>0.25</v>
+      </c>
+      <c r="C5">
+        <v>0.21111111111111111</v>
+      </c>
+      <c r="E5">
+        <f>D2+B5</f>
+        <v>0.78749999999999998</v>
+      </c>
+      <c r="G5">
+        <f>F2+C5</f>
+        <v>0.80069155016523441</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>0.2</v>
+      </c>
+      <c r="C6">
+        <v>0.2066870629370629</v>
+      </c>
+      <c r="E6">
+        <f>D2+B6</f>
+        <v>0.73750000000000004</v>
+      </c>
+      <c r="G6">
+        <f>F2+C6</f>
+        <v>0.79626750199118623</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>0.9375</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0.93162393162393098</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0.94100344100344102</v>
+      </c>
+      <c r="D8">
+        <v>0.93426943426943398</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="B14" s="5">
+        <v>0.94551282051282004</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0.95119463869463805</v>
+      </c>
+      <c r="D14">
+        <v>0.94744129176106695</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18">
+        <v>0.93</v>
+      </c>
+      <c r="C18">
+        <v>0.93117153664821017</v>
+      </c>
+      <c r="D18">
+        <v>0.9283088235294118</v>
+      </c>
+      <c r="E18">
+        <v>0.92847053390739809</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19">
+        <v>0.9375</v>
+      </c>
+      <c r="C19">
+        <v>0.94100344100344102</v>
+      </c>
+      <c r="D19">
+        <v>0.93162393162393176</v>
+      </c>
+      <c r="E19">
+        <v>0.93426943426943421</v>
       </c>
     </row>
   </sheetData>
